--- a/output/Data and Chart Outputs/north_macedonia_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/north_macedonia_power_generation_daily.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>North Macedonia power generation by type (ENTSO-E) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -888,7 +889,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-03 09:51 UTC; 2080 days, 2021-01-01 to 2026-10-02</t>
+          <t>2026-10-28 00:44 UTC; 2104 days, 2021-01-01 to 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2081"/>
+  <dimension ref="A1:P2105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106771,7 +106772,7 @@
         <v>0</v>
       </c>
       <c r="P2080" t="n">
-        <v>8579.5</v>
+        <v>9627.9</v>
       </c>
     </row>
     <row r="2081">
@@ -106779,7 +106780,7 @@
         <v>46297</v>
       </c>
       <c r="B2081" t="n">
-        <v>2672.6</v>
+        <v>2884.4</v>
       </c>
       <c r="C2081" t="n">
         <v>0</v>
@@ -106788,7 +106789,7 @@
         <v>0</v>
       </c>
       <c r="E2081" t="n">
-        <v>3092.1</v>
+        <v>3370.8</v>
       </c>
       <c r="F2081" t="n">
         <v>0</v>
@@ -106797,10 +106798,10 @@
         <v>0</v>
       </c>
       <c r="H2081" t="n">
-        <v>652</v>
+        <v>691.9</v>
       </c>
       <c r="I2081" t="n">
-        <v>1114.9</v>
+        <v>1153.5</v>
       </c>
       <c r="J2081" t="n">
         <v>0</v>
@@ -106812,13 +106813,1216 @@
         <v>0</v>
       </c>
       <c r="M2081" t="n">
-        <v>7531.6</v>
+        <v>8100.6</v>
       </c>
       <c r="N2081" t="n">
         <v>0</v>
       </c>
       <c r="O2081" t="n">
         <v>0</v>
+      </c>
+      <c r="P2081" t="n">
+        <v>9639.1</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B2082" t="n">
+        <v>2874.7</v>
+      </c>
+      <c r="C2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>3354.1</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2082" t="n">
+        <v>649</v>
+      </c>
+      <c r="I2082" t="n">
+        <v>1015.7</v>
+      </c>
+      <c r="J2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2082" t="n">
+        <v>7893.5</v>
+      </c>
+      <c r="N2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2082" t="n">
+        <v>9302.4</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2083" t="n">
+        <v>3554.9</v>
+      </c>
+      <c r="C2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>435.9</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>3343</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2083" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="I2083" t="n">
+        <v>1107</v>
+      </c>
+      <c r="J2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2083" t="n">
+        <v>8625.6</v>
+      </c>
+      <c r="N2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2083" t="n">
+        <v>9609.799999999999</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2084" t="n">
+        <v>3522.5</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>4894.5</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>3332.9</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2084" t="n">
+        <v>198.4</v>
+      </c>
+      <c r="I2084" t="n">
+        <v>900.7</v>
+      </c>
+      <c r="J2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2084" t="n">
+        <v>12849</v>
+      </c>
+      <c r="N2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2084" t="n">
+        <v>10234.8</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2085" t="n">
+        <v>3700.9</v>
+      </c>
+      <c r="C2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>4897.1</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>3332.8</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2085" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="I2085" t="n">
+        <v>862.9</v>
+      </c>
+      <c r="J2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2085" t="n">
+        <v>12998.1</v>
+      </c>
+      <c r="N2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2085" t="n">
+        <v>10515.1</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2086" t="n">
+        <v>3582.1</v>
+      </c>
+      <c r="C2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>4824.7</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>3256.6</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2086" t="n">
+        <v>263.3</v>
+      </c>
+      <c r="I2086" t="n">
+        <v>882.9</v>
+      </c>
+      <c r="J2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2086" t="n">
+        <v>12809.6</v>
+      </c>
+      <c r="N2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2086" t="n">
+        <v>11113.9</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2087" t="n">
+        <v>3556.6</v>
+      </c>
+      <c r="C2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>5022.2</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>3363.6</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2087" t="n">
+        <v>469.9</v>
+      </c>
+      <c r="I2087" t="n">
+        <v>679.6</v>
+      </c>
+      <c r="J2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2087" t="n">
+        <v>13091.9</v>
+      </c>
+      <c r="N2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2087" t="n">
+        <v>11430.2</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2088" t="n">
+        <v>4663.8</v>
+      </c>
+      <c r="C2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>5300.3</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>3331.2</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2088" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="I2088" t="n">
+        <v>451.8</v>
+      </c>
+      <c r="J2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2088" t="n">
+        <v>13837.7</v>
+      </c>
+      <c r="N2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2088" t="n">
+        <v>12697.6</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2089" t="n">
+        <v>3544</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>2951.8</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>3287.5</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2089" t="n">
+        <v>792.6</v>
+      </c>
+      <c r="I2089" t="n">
+        <v>808.3</v>
+      </c>
+      <c r="J2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2089" t="n">
+        <v>11384.2</v>
+      </c>
+      <c r="N2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2089" t="n">
+        <v>9730.200000000001</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2090" t="n">
+        <v>3569.2</v>
+      </c>
+      <c r="C2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>1786.6</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>3233</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2090" t="n">
+        <v>941.8</v>
+      </c>
+      <c r="I2090" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="J2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2090" t="n">
+        <v>9911.9</v>
+      </c>
+      <c r="N2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2090" t="n">
+        <v>12866.2</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2091" t="n">
+        <v>3737.6</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>4925.5</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>3338.3</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2091" t="n">
+        <v>2430.2</v>
+      </c>
+      <c r="I2091" t="n">
+        <v>466</v>
+      </c>
+      <c r="J2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2091" t="n">
+        <v>14897.6</v>
+      </c>
+      <c r="N2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2091" t="n">
+        <v>10338.6</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2092" t="n">
+        <v>6683.7</v>
+      </c>
+      <c r="C2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>5293.2</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>3314</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2092" t="n">
+        <v>2590</v>
+      </c>
+      <c r="I2092" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="J2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2092" t="n">
+        <v>18093.4</v>
+      </c>
+      <c r="N2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2092" t="n">
+        <v>16446.4</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2093" t="n">
+        <v>6117.1</v>
+      </c>
+      <c r="C2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>5415.6</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>3243</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2093" t="n">
+        <v>2667</v>
+      </c>
+      <c r="I2093" t="n">
+        <v>480</v>
+      </c>
+      <c r="J2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2093" t="n">
+        <v>17922.7</v>
+      </c>
+      <c r="N2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2093" t="n">
+        <v>15561.5</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2094" t="n">
+        <v>5595.6</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>5023</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>3279.3</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2094" t="n">
+        <v>2526</v>
+      </c>
+      <c r="I2094" t="n">
+        <v>741.5</v>
+      </c>
+      <c r="J2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2094" t="n">
+        <v>17165.4</v>
+      </c>
+      <c r="N2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2094" t="n">
+        <v>14549.5</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2095" t="n">
+        <v>6318.9</v>
+      </c>
+      <c r="C2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>5373.4</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>3266.2</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2095" t="n">
+        <v>1756.3</v>
+      </c>
+      <c r="I2095" t="n">
+        <v>487.4</v>
+      </c>
+      <c r="J2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2095" t="n">
+        <v>17202.2</v>
+      </c>
+      <c r="N2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2095" t="n">
+        <v>15349.4</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2096" t="n">
+        <v>5576.2</v>
+      </c>
+      <c r="C2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>4788</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>3279.9</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2096" t="n">
+        <v>1625.9</v>
+      </c>
+      <c r="I2096" t="n">
+        <v>757.1</v>
+      </c>
+      <c r="J2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2096" t="n">
+        <v>16027.1</v>
+      </c>
+      <c r="N2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2096" t="n">
+        <v>14551.2</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2097" t="n">
+        <v>5957.4</v>
+      </c>
+      <c r="C2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>5329.2</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>3325.7</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2097" t="n">
+        <v>1592.5</v>
+      </c>
+      <c r="I2097" t="n">
+        <v>717.8</v>
+      </c>
+      <c r="J2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2097" t="n">
+        <v>16922.5</v>
+      </c>
+      <c r="N2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2097" t="n">
+        <v>16203.7</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2098" t="n">
+        <v>3794.1</v>
+      </c>
+      <c r="C2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>4903.4</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>5048.5</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2098" t="n">
+        <v>1689.1</v>
+      </c>
+      <c r="I2098" t="n">
+        <v>889.9</v>
+      </c>
+      <c r="J2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2098" t="n">
+        <v>16325</v>
+      </c>
+      <c r="N2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2098" t="n">
+        <v>13089.6</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2099" t="n">
+        <v>5299.1</v>
+      </c>
+      <c r="C2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>5097.6</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>4079.8</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2099" t="n">
+        <v>683.4</v>
+      </c>
+      <c r="I2099" t="n">
+        <v>908.5</v>
+      </c>
+      <c r="J2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2099" t="n">
+        <v>16068.4</v>
+      </c>
+      <c r="N2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2099" t="n">
+        <v>13302</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2100" t="n">
+        <v>5732.8</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>5170.8</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>3329.1</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2100" t="n">
+        <v>1315.3</v>
+      </c>
+      <c r="I2100" t="n">
+        <v>522.3</v>
+      </c>
+      <c r="J2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2100" t="n">
+        <v>16070.2</v>
+      </c>
+      <c r="N2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2100" t="n">
+        <v>14483.4</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>4220.7</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>4913.6</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>3295</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2101" t="n">
+        <v>875.9</v>
+      </c>
+      <c r="I2101" t="n">
+        <v>676.7</v>
+      </c>
+      <c r="J2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2101" t="n">
+        <v>13981.8</v>
+      </c>
+      <c r="N2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2101" t="n">
+        <v>13925.2</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>3795.5</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>5043.7</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>3260.2</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2102" t="n">
+        <v>1871.2</v>
+      </c>
+      <c r="I2102" t="n">
+        <v>693.4</v>
+      </c>
+      <c r="J2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2102" t="n">
+        <v>14663.9</v>
+      </c>
+      <c r="N2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2102" t="n">
+        <v>12290.9</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>4444.6</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>571.7</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>3252.1</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2103" t="n">
+        <v>432.5</v>
+      </c>
+      <c r="I2103" t="n">
+        <v>650.5</v>
+      </c>
+      <c r="J2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2103" t="n">
+        <v>9351.5</v>
+      </c>
+      <c r="N2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2103" t="n">
+        <v>12881.7</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>4987.6</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>5171.5</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>3328.8</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2104" t="n">
+        <v>301.2</v>
+      </c>
+      <c r="I2104" t="n">
+        <v>336.6</v>
+      </c>
+      <c r="J2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2104" t="n">
+        <v>14125.6</v>
+      </c>
+      <c r="N2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2104" t="n">
+        <v>16300.4</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>5211.1</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>4909.6</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>3235.5</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2105" t="n">
+        <v>1523.3</v>
+      </c>
+      <c r="I2105" t="n">
+        <v>239.4</v>
+      </c>
+      <c r="J2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2105" t="n">
+        <v>15118.9</v>
+      </c>
+      <c r="N2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2105" t="n">
+        <v>16674</v>
       </c>
     </row>
   </sheetData>
